--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92569516943</v>
+        <v>46157.93101568142</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93101568142</v>
+        <v>46157.93175057502</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93175057502</v>
+        <v>46157.93401098032</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93401098032</v>
+        <v>46157.93719053076</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93719053076</v>
+        <v>46158.28217269458</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28217269458</v>
+        <v>46158.29682929493</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29682929493</v>
+        <v>46158.29815887885</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29815887885</v>
+        <v>46158.33388273668</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33388273668</v>
+        <v>46158.3685809599</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3685809599</v>
+        <v>46158.37288722835</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
